--- a/代号童话（策划资料）/01-系统设计/.xlsx
+++ b/代号童话（策划资料）/01-系统设计/.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hexiying\Desktop\工作文件夹\AI-游戏\魔法卡片\01-系统\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hexiying\Desktop\工作文件夹\数值\关卡设计\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="demo" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet5" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet7" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="370">
   <si>
     <t>📜 游戏概况</t>
   </si>
@@ -589,6 +592,564 @@
   </si>
   <si>
     <t>高级卡片只能在炼卡炉里炼制获得。炼制卡片需要按一定的规则进行，炼卡将消耗玩家放入的素材卡，且需要等待一定时间。玩家一次可以将三张卡片放入炼卡炉，但同时只能炼制一张卡片，后面的卡片自动排期，在前面的卡片炼制完成后自动开始炼制。炼制完成后玩家可以获得炼制的卡片及一定经验值。</t>
+  </si>
+  <si>
+    <t>一、核心循环：闭环生态链</t>
+  </si>
+  <si>
+    <t>你的设想已经形成了一个完美的资源-行动-成长飞轮：</t>
+  </si>
+  <si>
+    <t>系统抽卡（根基）：每半小时产出基础素材，保证玩家永远有事做，是离线收益的保底。</t>
+  </si>
+  <si>
+    <t>炼卡扩张（成长）：消耗素材炼出【土地卡】，领地越大，能摆放的建筑、种植的植物就越多，生产力上限越高。</t>
+  </si>
+  <si>
+    <t>搜打撤副本（引擎）：通过传送门进入副本，快速获取大量稀有素材、特殊道具和图纸，这是爆发式成长的来源。</t>
+  </si>
+  <si>
+    <t>回收+兑换（经济）：副本里带出来的“战利品”交给系统回收，换成通用资金，再兑换成独一无二的【特殊图纸】。这就形成了“战斗→经济→科技”的递进。</t>
+  </si>
+  <si>
+    <t>二、土地扩张：领地的“实感化”</t>
+  </si>
+  <si>
+    <t>不再只是一片空地，每一块土地都有价值。</t>
+  </si>
+  <si>
+    <t>土地卡合成公式：3张【土系素材】+ 1张【水源素材】+ 1张【风系素材】= 1张【可耕种土地卡】。炼卡时间需要30分钟，让扩张带有仪式感。</t>
+  </si>
+  <si>
+    <t>领地等级系统：你拥有的土地数量决定你的“领地等级”。</t>
+  </si>
+  <si>
+    <t>1级领地（初始1块地）：只能造1个炼卡炉，1个仓库。</t>
+  </si>
+  <si>
+    <t>5级领地（拥有5块地）：解锁【哨塔】功能，能预警副本入口的怪物强度。</t>
+  </si>
+  <si>
+    <t>10级领地（拥有10块地）：解锁【传送门稳定器】，可以锁定一个副本坐标，永久开启传送。</t>
+  </si>
+  <si>
+    <t>地块附魔：利用不同元素素材给土地“施肥”，可以改变其属性。比如把一块地变成【火属性地块】，在这块地上炼火系卡片，时间缩短20%；在这块地上种植物，收获数量+1。</t>
+  </si>
+  <si>
+    <t>三、“搜打撤”副本循环设计（核心爽点）</t>
+  </si>
+  <si>
+    <t>传送门机制：靠近领地内的【传送门】弹出界面，显示当前可进入的副本列表。副本分为三种类型，分别对应“搜”、“打”、“撤”的侧重点：</t>
+  </si>
+  <si>
+    <t>副本类型</t>
+  </si>
+  <si>
+    <t>核心目标</t>
+  </si>
+  <si>
+    <t>主要产出</t>
+  </si>
+  <si>
+    <t>风险/策略</t>
+  </si>
+  <si>
+    <t>探索类（搜）</t>
+  </si>
+  <si>
+    <t>生存与采集</t>
+  </si>
+  <si>
+    <t>稀有植物卡、矿物素材、宝箱（需炼金钥匙开启）</t>
+  </si>
+  <si>
+    <t>地图有迷雾，行动力有限，搜满背包必须“撤”，否则体力耗尽会昏迷，损失部分素材。</t>
+  </si>
+  <si>
+    <t>讨伐类（打）</t>
+  </si>
+  <si>
+    <t>战斗与击杀</t>
+  </si>
+  <si>
+    <t>怪物核心（紫色素材）、武器卡碎片、大量资金</t>
+  </si>
+  <si>
+    <t>BOSS有狂暴时间，必须在时间内击杀。考验你的召唤卡和临时炼制的“增幅药剂卡”。</t>
+  </si>
+  <si>
+    <t>秘境类（撤）</t>
+  </si>
+  <si>
+    <t>限时跑酷与逃生</t>
+  </si>
+  <si>
+    <t>高价值“时空沙漏”（可立即完成当前炼卡）、特殊建材</t>
+  </si>
+  <si>
+    <t>进入后倒计时开始，5分钟内必须抵达撤离点。路上有大量稀有矿，但怪物会不断追击。“贪还是不贪”是核心博弈。</t>
+  </si>
+  <si>
+    <t>四、系统回收与资金商店（经济闭环）</t>
+  </si>
+  <si>
+    <t>这个设计解决了“垃圾卡”和“溢出资源”的最终归宿。</t>
+  </si>
+  <si>
+    <t>回收定价策略：不只是简单卖钱，可以根据当前炼卡需求动态调整。</t>
+  </si>
+  <si>
+    <t>常规回收：任意卡片拖入回收界面，获得固定资金。</t>
+  </si>
+  <si>
+    <t>限时高价回收：系统会发布“订单”，比如“今日急需【火系素材】30张，回收价提升50%”。这引导玩家有针对性地去刷副本或开特定卡包。</t>
+  </si>
+  <si>
+    <t>特殊图纸商店（核心驱动力）：资金在这里兑换的不是现成道具，而是“蓝图”。</t>
+  </si>
+  <si>
+    <t>功能型图纸：【自动采集器蓝图】（建造后，领地内的植物成熟自动收获）、【双倍炼卡炉蓝图】（一次可以炼两炉）。</t>
+  </si>
+  <si>
+    <t>装饰型图纸：【石质围墙蓝图】、【哥特式尖顶蓝图】，这些不只是好看，组合摆放能提升“领地繁荣度”，解锁更多系统福利。</t>
+  </si>
+  <si>
+    <t>限定召唤图纸：【龙蛋召唤卷轴碎片】，集齐10个碎片可兑换完整卷轴，召唤一只传奇生物，能帮你巡逻领地，甚至陪你下副本。</t>
+  </si>
+  <si>
+    <t>五、你的“异世界角色”设定（赋予灵魂）</t>
+  </si>
+  <si>
+    <t>结合以上所有玩法，你的角色不应该只是一个“操作者”，他需要有明确的成长路径和身份：</t>
+  </si>
+  <si>
+    <t>角色初始背景：</t>
+  </si>
+  <si>
+    <t>你是一个来自现代世界的“炼金遗孤”，醒来时只记得自己是个游戏策划（笑）。你手上的“系统”其实是这个世界古代文明留下的“炼金网络终端”。你的优势不是武力，而是“对‘配方’和‘效率’的直觉理解”——你能看到卡片之间的隐藏关联。</t>
+  </si>
+  <si>
+    <t>角色核心成长属性（与玩法挂钩）：</t>
+  </si>
+  <si>
+    <t>不同于传统的“等级”，你的成长体现在三个可升级的“灵魂天赋”上：</t>
+  </si>
+  <si>
+    <t>【感知】（影响“搜”）：</t>
+  </si>
+  <si>
+    <t>提升后，在探索副本时，地图上的隐藏宝箱和稀有矿脉会发出微光提示。满级时甚至能看到“怪物仇恨范围”。</t>
+  </si>
+  <si>
+    <t>升级方式：成功撤离副本10次。</t>
+  </si>
+  <si>
+    <t>【共鸣】（影响“炼”）：</t>
+  </si>
+  <si>
+    <t>提升后，炼卡时有一定概率“暴击”——投入3张素材，产出2张高级卡（多出一张！）。或者缩短炼卡时间。</t>
+  </si>
+  <si>
+    <t>升级方式：炼成特定数量的高级卡片（如紫卡、金卡）。</t>
+  </si>
+  <si>
+    <t>【意志】（影响“打”与“种”）：</t>
+  </si>
+  <si>
+    <t>提升后，召唤物（战斗伙伴）属性提升，植物生长周期缩短，且收获时有概率出现“变种”。</t>
+  </si>
+  <si>
+    <t>升级方式：击杀精英怪物，或收获稀有植物。</t>
+  </si>
+  <si>
+    <t>角色随身装备（不是抽的，是“养成的”）：</t>
+  </si>
+  <si>
+    <t>炼金手册：初始是一本破书，随着你炼出新卡片，它会自动记录配方。你可以在手册里“标记”想合成的卡，系统会提示你当前还缺哪些素材，相当于内置任务指引。</t>
+  </si>
+  <si>
+    <t>空间戒指：初始只有10格背包（只能装卡片）。通过炼卡或商店购买【扩容宝石】，可以扩展到50格。这是下副本“搜”的最核心硬件。</t>
+  </si>
+  <si>
+    <t>六、一个完整的“搜打撤”日流程示例</t>
+  </si>
+  <si>
+    <t>早上9点：上线，收菜（植物卡成熟），收炉子（昨晚放的3张【铁矿】炼成【精铁卡】）。用【精铁卡】+【木材卡】炼成1张【土地卡】（耗时1小时）。</t>
+  </si>
+  <si>
+    <t>9点半：系统发了一张【火系素材】，正好凑够3张，丢进炉子炼【火焰结晶】（备货）。</t>
+  </si>
+  <si>
+    <t>10点：土地卡炼好！使用后领地扩张一块。把新地划为“武器工坊”用地。</t>
+  </si>
+  <si>
+    <t>10点半：传送门能量充满。选择“秘境类”副本进入。</t>
+  </si>
+  <si>
+    <t>搜：前3分钟疯狂采集一种叫“月光草”的稀有植物。</t>
+  </si>
+  <si>
+    <t>打：遭遇守护怪物，使用之前召唤的【石像鬼卡】抵挡，配合自己炼的【燃烧瓶卡】击杀。</t>
+  </si>
+  <si>
+    <t>撤：还剩1分钟，背包满了（全是月光草+怪物核心），果断冲向撤离点。成功！</t>
+  </si>
+  <si>
+    <t>11点：将“月光草”卖给系统，发现今天是“月光草高价日”！赚了500资金。</t>
+  </si>
+  <si>
+    <t>11点半：去商店兑换了一张【熔炉加速器蓝图】。研究了一下，需要【精铁卡】x10 + 【火系结晶】x5 才能造。目标确立：未来两天，主刷火系副本，把加速器造出来！</t>
+  </si>
+  <si>
+    <t>这样，整个游戏的节奏就是：日常挂机攒基础卡 → 针对性地炼卡扩张/造建筑 → 组织资源下副本刷特定素材 → 回收换钱买图纸 → 变强后再挑战更难副本。</t>
+  </si>
+  <si>
+    <t>这个框架已经非常扎实了。你觉得接下来需要优先设计哪个部分的具体细节？是副本里的具体遭遇事件，还是炼金炉的配方图谱系统，或者是召唤物的养成和指挥方式？我们可以挑一个深入“熔炼”一下！</t>
+  </si>
+  <si>
+    <t>一、种植产出的真实定位：它不只是“商品”，更是“工业原料”和“战略物资”</t>
+  </si>
+  <si>
+    <t>要赋予种植不可替代的价值，核心思路是：种植产出的是“基础工业品”和“消耗品”，而副本产出的是“高级半成品”和“稀有通货”。</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>代表产出</t>
+  </si>
+  <si>
+    <t>核心用途</t>
+  </si>
+  <si>
+    <t>回收价格（金币）</t>
+  </si>
+  <si>
+    <t>粮食类</t>
+  </si>
+  <si>
+    <t>小麦、水稻、土豆</t>
+  </si>
+  <si>
+    <t>炼卡合成【基础口粮卡】——这是召唤物（战斗伙伴）的“维持费”，没有口粮，它们会罢工甚至叛变。</t>
+  </si>
+  <si>
+    <t>低（系统无限收，保底收入）</t>
+  </si>
+  <si>
+    <t>药草类</t>
+  </si>
+  <si>
+    <t>止血草、魔力花</t>
+  </si>
+  <si>
+    <t>炼卡合成【初级药水卡】——下副本的硬通货，不带药水等于送死。种得越多，下本越省心。</t>
+  </si>
+  <si>
+    <t>中（但通常玩家舍不得卖，自用更划算）</t>
+  </si>
+  <si>
+    <t>经济作物</t>
+  </si>
+  <si>
+    <t>棉麻、橡胶树</t>
+  </si>
+  <si>
+    <t>炼卡合成【布料卡】、【软管卡】——升级建筑（比如扩大仓库、升级炼卡炉）的必须建材。</t>
+  </si>
+  <si>
+    <t>中（但直接卖亏了，加工后再卖价值翻倍）</t>
+  </si>
+  <si>
+    <t>特殊作物</t>
+  </si>
+  <si>
+    <t>荧光菇、雷击木</t>
+  </si>
+  <si>
+    <t>炼卡合成【探照灯卡】、【避雷针卡】——专门用来应对副本中的特定环境DEBUFF（如黑暗、雷暴）。</t>
+  </si>
+  <si>
+    <t>高（但产量极低，仅供自用或高价挂单）</t>
+  </si>
+  <si>
+    <t>关键结论：种菜的第一优先级不是卖钱，而是“自产自销，支撑炼卡和战斗链条”。只有当你的产出远超自用需求时，才考虑出售。</t>
+  </si>
+  <si>
+    <t>二、玩家获取金币（资金）的三条并行管道（各有侧重点）</t>
+  </si>
+  <si>
+    <t>为了让你更清晰，我们把金币获取分为三条渠道，它们节奏不同、风险不同、效率不同，玩家会根据自己的在线时间和喜好侧重不同路线。</t>
+  </si>
+  <si>
+    <t>获取渠道</t>
+  </si>
+  <si>
+    <t>核心操作</t>
+  </si>
+  <si>
+    <t>收益频率</t>
+  </si>
+  <si>
+    <t>风险/成本</t>
+  </si>
+  <si>
+    <t>收益上限</t>
+  </si>
+  <si>
+    <t>适合玩家类型</t>
+  </si>
+  <si>
+    <t>种植回收</t>
+  </si>
+  <si>
+    <t>种菜→收获→直接丢系统回收</t>
+  </si>
+  <si>
+    <t>低（每天2-4次收菜）</t>
+  </si>
+  <si>
+    <t>极低（只需上线收菜）</t>
+  </si>
+  <si>
+    <t>低（稳定但慢）</t>
+  </si>
+  <si>
+    <t>佛系/碎片时间玩家，主要用来维持日常开支。</t>
+  </si>
+  <si>
+    <t>副本搜打撤</t>
+  </si>
+  <si>
+    <t>进本→采集/战斗→带回战利品→回收</t>
+  </si>
+  <si>
+    <t>高（每小时可刷1-2次）</t>
+  </si>
+  <si>
+    <t>高（可能重伤、损失物资、甚至白给）</t>
+  </si>
+  <si>
+    <t>极高（欧皇一发出稀有材料）</t>
+  </si>
+  <si>
+    <t>肝帝/操作型玩家，享受高风险高回报。</t>
+  </si>
+  <si>
+    <t>炼卡加工增值</t>
+  </si>
+  <si>
+    <t>把种出来的菜炼成高级卡，再卖给系统</t>
+  </si>
+  <si>
+    <t>中（取决于炉子和配方）</t>
+  </si>
+  <si>
+    <t>中（需要先投入素材和时间）</t>
+  </si>
+  <si>
+    <t>高（差价利润可观）</t>
+  </si>
+  <si>
+    <t>策略型/挂机型玩家，靠“炼金术”发家致富</t>
+  </si>
+  <si>
+    <t>三、让“种菜卖钱”本身也充满策略性（不只是无脑回收）</t>
+  </si>
+  <si>
+    <t>如果“回收”只是简单丢进去换钱，确实无聊。我们可以加入两个机制让种菜直接变现变得有趣且需要思考：</t>
+  </si>
+  <si>
+    <t>1. 系统“限时高价收购订单”（每日刷新）</t>
+  </si>
+  <si>
+    <t>每天早上8点，系统会发布3个“收购订单”。</t>
+  </si>
+  <si>
+    <t>例如：“今日特需：【火焰椒】30个，收购价提升200%！”</t>
+  </si>
+  <si>
+    <t>玩家看到后，会去规划：“我有两块地空着，马上种火焰椒，8小时后成熟，正好赶上订单截止时间！”——这变成了一个需要预判和规划的“种田期货”玩法。</t>
+  </si>
+  <si>
+    <t>2. “新鲜度”机制（让出售时机变重要）</t>
+  </si>
+  <si>
+    <t>植物收获后，有一个“新鲜度”条（从100%逐渐下降）。</t>
+  </si>
+  <si>
+    <t>新鲜度100%-80%：出售价格150%。</t>
+  </si>
+  <si>
+    <t>新鲜度80%-50%：出售价格100%。</t>
+  </si>
+  <si>
+    <t>新鲜度50%以下：出售价格50%，且不能再用于炼卡（只能卖）。</t>
+  </si>
+  <si>
+    <t>这就逼迫玩家：要么及时上线收菜卖高价，要么炼成卡锁住价值。 增加了“何时卖”的决策博弈。</t>
+  </si>
+  <si>
+    <t>四、一个完整的“种菜→加工→回收”增值链条示例</t>
+  </si>
+  <si>
+    <t>让玩家亲眼看到“种菜 + 炼卡 = 暴利”，才能真正点燃他们种田的热情。</t>
+  </si>
+  <si>
+    <t>基础链条：</t>
+  </si>
+  <si>
+    <t>种：种下【小麦种子】→ 4小时后收获 【小麦素材】×3。</t>
+  </si>
+  <si>
+    <t>炼：将3张【小麦素材】放入炼卡炉，消耗10分钟 → 炼成1张 【面粉素材】。</t>
+  </si>
+  <si>
+    <t>再炼：将1张【面粉素材】+ 1张【水素材】+ 1张【糖素材】（糖可从副本或商店获取）→ 炼成1张 【面包卡】。</t>
+  </si>
+  <si>
+    <t>卖：【面包卡】直接回收给系统，价格是【小麦素材】单价的5倍。</t>
+  </si>
+  <si>
+    <t>策略点：玩家可以选择：</t>
+  </si>
+  <si>
+    <t>懒人玩法：收获小麦直接卖，赚1倍的钱，立刻到手。</t>
+  </si>
+  <si>
+    <t>精加工玩法：花时间、花炉子、凑齐辅料，炼成面包再卖，赚5倍的钱。（但占用炉子时间，可能会耽误炼其他急需的卡）</t>
+  </si>
+  <si>
+    <t>这就是“时间/资源/机会成本”的三重博弈，让种田彻底脱离“无脑点击”的范畴。</t>
+  </si>
+  <si>
+    <t>五、最终的“金币用途”闭环（让钱永远不够花）</t>
+  </si>
+  <si>
+    <t>为了避免玩家后期金币溢出，失去动力，我们要设置足够多且持续消耗金币的“资金黑洞”：</t>
+  </si>
+  <si>
+    <t>消耗方向</t>
+  </si>
+  <si>
+    <t>具体内容</t>
+  </si>
+  <si>
+    <t>价格梯度</t>
+  </si>
+  <si>
+    <t>商店特殊图纸</t>
+  </si>
+  <si>
+    <t>之前提到的【自动采集器】、【双倍炉】、【龙蛋卷轴碎片】</t>
+  </si>
+  <si>
+    <t>极高，需要长期积累</t>
+  </si>
+  <si>
+    <t>传送门充能</t>
+  </si>
+  <si>
+    <t>每次进入副本需要消耗“传送能量”，可用金币直接购买（相当于体力机制）</t>
+  </si>
+  <si>
+    <t>按次收费，越高级副本越贵</t>
+  </si>
+  <si>
+    <t>建筑维护费</t>
+  </si>
+  <si>
+    <t>高级建筑（如自动采集器）会随时间损耗，需用金币购买“维修包”</t>
+  </si>
+  <si>
+    <t>每日小额但持续</t>
+  </si>
+  <si>
+    <t>召唤物复活</t>
+  </si>
+  <si>
+    <t>如果你带下本的召唤物战死了，需要金币在“英灵殿”复活它</t>
+  </si>
+  <si>
+    <t>按稀有度收费，传说级极贵</t>
+  </si>
+  <si>
+    <t>外观/装饰</t>
+  </si>
+  <si>
+    <t>纯粹的个性化装修，满足收集癖和展示欲</t>
+  </si>
+  <si>
+    <t>无底洞</t>
+  </si>
+  <si>
+    <t>这样，玩家会永远处于 “想买的东西很多，但钱总是不够” 的状态，从而驱动他们不断在 “种菜稳赚” 和 “副本暴富” 之间灵活切换。</t>
+  </si>
+  <si>
+    <t>抽卡系统（定时发卡）</t>
+  </si>
+  <si>
+    <t>炼卡系统（核心合成）</t>
+  </si>
+  <si>
+    <t>种植系统（植物卡）</t>
+  </si>
+  <si>
+    <t>建筑系统（建筑卡）</t>
+  </si>
+  <si>
+    <t>召唤系统（召唤卡）</t>
+  </si>
+  <si>
+    <t>副本系统（搜打撤）</t>
+  </si>
+  <si>
+    <t>经济系统（回收与商店）</t>
+  </si>
+  <si>
+    <t>领地系统（土地扩张）</t>
+  </si>
+  <si>
+    <t>角色成长系统（灵魂天赋）</t>
+  </si>
+  <si>
+    <t>目标与收集系统（图鉴、剧情等）</t>
+  </si>
+  <si>
+    <t>战斗系统</t>
+  </si>
+  <si>
+    <t>具体设计</t>
+  </si>
+  <si>
+    <t>玩家攻击方式</t>
+  </si>
+  <si>
+    <t>俯视角自由射击（鼠标瞄准/摇杆瞄准），单发伤害=1，主要用于触发、引怪、补刀。</t>
+  </si>
+  <si>
+    <t>技能卡系统</t>
+  </si>
+  <si>
+    <t>下本前从仓库选择技能卡装入4个技能槽（如：火球、冰环、治疗、护盾）。副本中按快捷键释放，每张卡使用后消失。技能卡由炼卡炉生产。</t>
+  </si>
+  <si>
+    <t>永久召唤物</t>
+  </si>
+  <si>
+    <t>随行提供被动光环（如攻击+20%、防御+15%）。无AI、无主动攻击。召唤后存活24小时，可投喂口粮延长。无需复杂AI开发。</t>
+  </si>
+  <si>
+    <t>临时召唤卡</t>
+  </si>
+  <si>
+    <t>副本内可使用的消耗品卡，使用后召唤一只AI仆从（自动攻击最近敌人），持续60秒后消失。简单AI（移动→攻击）即可，无需复杂逻辑。</t>
+  </si>
+  <si>
+    <t>搜打撤节奏</t>
+  </si>
+  <si>
+    <t>下本前炼满技能卡和临时召唤卡 → 副本中射击+丢技能+适时召唤炮灰 → 撤离结算 → 资源消耗完毕 → 回领地种田/炼卡准备下一趟</t>
   </si>
 </sst>
 </file>
@@ -1511,6 +2072,53 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="12515850"/>
+          <a:ext cx="4371975" cy="4619625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -3285,4 +3893,841 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D104"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E14" t="s">
+        <v>284</v>
+      </c>
+      <c r="F14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" t="s">
+        <v>288</v>
+      </c>
+      <c r="D15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>290</v>
+      </c>
+      <c r="F15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F17" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>329</v>
+      </c>
+      <c r="B64" t="s">
+        <v>330</v>
+      </c>
+      <c r="C64" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>332</v>
+      </c>
+      <c r="B65" t="s">
+        <v>333</v>
+      </c>
+      <c r="C65" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>335</v>
+      </c>
+      <c r="B66" t="s">
+        <v>336</v>
+      </c>
+      <c r="C66" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>338</v>
+      </c>
+      <c r="B67" t="s">
+        <v>339</v>
+      </c>
+      <c r="C67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>341</v>
+      </c>
+      <c r="B68" t="s">
+        <v>342</v>
+      </c>
+      <c r="C68" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>344</v>
+      </c>
+      <c r="B69" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>347</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>358</v>
+      </c>
+      <c r="B24" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>364</v>
+      </c>
+      <c r="B27" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B28" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>368</v>
+      </c>
+      <c r="B29" t="s">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>